--- a/output/roomself_excel/11651.xlsx
+++ b/output/roomself_excel/11651.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>109461</v>
+        <v>145700</v>
       </c>
       <c r="D2" t="n">
-        <v>2648</v>
+        <v>3120</v>
       </c>
       <c r="E2" t="n">
-        <v>367</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>347</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -492,16 +492,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>435366</v>
+        <v>274064</v>
       </c>
       <c r="D3" t="n">
-        <v>10564</v>
+        <v>5712</v>
       </c>
       <c r="E3" t="n">
-        <v>756</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>645</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -514,16 +514,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>48240</v>
+        <v>109461</v>
       </c>
       <c r="D4" t="n">
-        <v>1764</v>
+        <v>2648</v>
       </c>
       <c r="E4" t="n">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -536,16 +536,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>42612</v>
+        <v>48240</v>
       </c>
       <c r="D5" t="n">
-        <v>1652</v>
+        <v>1764</v>
       </c>
       <c r="E5" t="n">
-        <v>238</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>227</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -558,16 +558,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>111848</v>
+        <v>42612</v>
       </c>
       <c r="D6" t="n">
-        <v>2676</v>
+        <v>1652</v>
       </c>
       <c r="E6" t="n">
-        <v>328</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>69598</v>
+        <v>111848</v>
       </c>
       <c r="D7" t="n">
-        <v>2464</v>
+        <v>2676</v>
       </c>
       <c r="E7" t="n">
-        <v>356</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>184</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -598,14 +598,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16786</v>
+        <v>117986</v>
       </c>
       <c r="D8" t="n">
-        <v>1052</v>
+        <v>2748</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -624,16 +624,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>19550</v>
+        <v>16786</v>
       </c>
       <c r="D9" t="n">
-        <v>1140</v>
+        <v>1052</v>
       </c>
       <c r="E9" t="n">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>30360</v>
+        <v>19550</v>
       </c>
       <c r="D10" t="n">
-        <v>1396</v>
+        <v>1140</v>
       </c>
       <c r="E10" t="n">
-        <v>184</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -686,20 +686,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>218544</v>
+        <v>42218</v>
       </c>
       <c r="D12" t="n">
-        <v>5052</v>
+        <v>1644</v>
       </c>
       <c r="E12" t="n">
-        <v>776</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>523</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -708,20 +708,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>117986</v>
+        <v>14364</v>
       </c>
       <c r="D13" t="n">
-        <v>2748</v>
+        <v>964</v>
       </c>
       <c r="E13" t="n">
-        <v>387</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>372</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>24244</v>
+        <v>69598</v>
       </c>
       <c r="D14" t="n">
-        <v>1300</v>
+        <v>2464</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -752,14 +752,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22768</v>
+        <v>30360</v>
       </c>
       <c r="D15" t="n">
-        <v>1276</v>
+        <v>1396</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -774,20 +774,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>145700</v>
+        <v>24244</v>
       </c>
       <c r="D16" t="n">
-        <v>3120</v>
+        <v>1300</v>
       </c>
       <c r="E16" t="n">
-        <v>486</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -800,10 +800,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>165</v>
+        <v>161302</v>
       </c>
       <c r="D17" t="n">
-        <v>104</v>
+        <v>5672</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -818,20 +818,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>42218</v>
+        <v>218544</v>
       </c>
       <c r="D18" t="n">
-        <v>1644</v>
+        <v>5052</v>
       </c>
       <c r="E18" t="n">
-        <v>209</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -844,16 +844,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>40018</v>
+        <v>22768</v>
       </c>
       <c r="D19" t="n">
-        <v>1620</v>
+        <v>1276</v>
       </c>
       <c r="E19" t="n">
-        <v>203</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -866,10 +866,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>253</v>
+        <v>165</v>
       </c>
       <c r="D20" t="n">
-        <v>136</v>
+        <v>104</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -884,20 +884,42 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>14364</v>
+        <v>40018</v>
       </c>
       <c r="D21" t="n">
-        <v>964</v>
+        <v>1620</v>
       </c>
       <c r="E21" t="n">
-        <v>133</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>86</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>253</v>
+      </c>
+      <c r="D22" t="n">
+        <v>136</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/11651.xlsx
+++ b/output/roomself_excel/11651.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,16 +449,6 @@
           <t>Perimeter</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>ExtWallLength</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>ExtWallWidth</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -475,12 +465,6 @@
       <c r="D2" t="n">
         <v>3120</v>
       </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +481,6 @@
       <c r="D3" t="n">
         <v>5712</v>
       </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +497,6 @@
       <c r="D4" t="n">
         <v>2648</v>
       </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +513,6 @@
       <c r="D5" t="n">
         <v>1764</v>
       </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +529,6 @@
       <c r="D6" t="n">
         <v>1652</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +545,6 @@
       <c r="D7" t="n">
         <v>2676</v>
       </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +561,6 @@
       <c r="D8" t="n">
         <v>2748</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +577,6 @@
       <c r="D9" t="n">
         <v>1052</v>
       </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +593,6 @@
       <c r="D10" t="n">
         <v>1140</v>
       </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +609,6 @@
       <c r="D11" t="n">
         <v>1376</v>
       </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +625,6 @@
       <c r="D12" t="n">
         <v>1644</v>
       </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +641,6 @@
       <c r="D13" t="n">
         <v>964</v>
       </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +657,6 @@
       <c r="D14" t="n">
         <v>2464</v>
       </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,12 +673,6 @@
       <c r="D15" t="n">
         <v>1396</v>
       </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,12 +689,6 @@
       <c r="D16" t="n">
         <v>1300</v>
       </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -805,12 +705,6 @@
       <c r="D17" t="n">
         <v>5672</v>
       </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -827,12 +721,6 @@
       <c r="D18" t="n">
         <v>5052</v>
       </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -849,12 +737,6 @@
       <c r="D19" t="n">
         <v>1276</v>
       </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -871,12 +753,6 @@
       <c r="D20" t="n">
         <v>104</v>
       </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -893,12 +769,6 @@
       <c r="D21" t="n">
         <v>1620</v>
       </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -914,12 +784,6 @@
       </c>
       <c r="D22" t="n">
         <v>136</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/11651.xlsx
+++ b/output/roomself_excel/11651.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
